--- a/data/analysis_pixtral_12b_no_reid/summary.xlsx
+++ b/data/analysis_pixtral_12b_no_reid/summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>provider</t>
   </si>
@@ -35,12 +35,6 @@
   </si>
   <si>
     <t>FN</t>
-  </si>
-  <si>
-    <t>support</t>
-  </si>
-  <si>
-    <t>VPI</t>
   </si>
   <si>
     <t>pixtral_12b_no_reid</t>
@@ -50,8 +44,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -67,7 +69,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,12 +77,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -375,65 +395,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B2">
+        <v>0.724</v>
+      </c>
+      <c r="C2">
+        <v>0.7</v>
+      </c>
+      <c r="D2">
+        <v>0.712</v>
+      </c>
+      <c r="E2">
+        <v>21</v>
+      </c>
+      <c r="F2">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="G2">
         <v>9</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>30</v>
-      </c>
-      <c r="H2">
-        <v>41</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_pixtral_12b_no_reid/summary.xlsx
+++ b/data/analysis_pixtral_12b_no_reid/summary.xlsx
@@ -14,9 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>provider</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>visual</t>
+  </si>
+  <si>
+    <t>reid</t>
   </si>
   <si>
     <t>precision</t>
@@ -37,23 +40,21 @@
     <t>FN</t>
   </si>
   <si>
-    <t>pixtral_12b_no_reid</t>
+    <t>support</t>
+  </si>
+  <si>
+    <t>VPI</t>
+  </si>
+  <si>
+    <t>pixtral_12b</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -69,7 +70,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -77,30 +78,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -395,53 +378,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="B2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.724</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.7</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.712</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>21</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>8</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>9</v>
+      </c>
+      <c r="I2">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>636</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_pixtral_12b_no_reid/summary.xlsx
+++ b/data/analysis_pixtral_12b_no_reid/summary.xlsx
@@ -53,8 +53,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -70,7 +78,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -78,12 +86,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,34 +408,34 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -421,19 +447,19 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.724</v>
+        <v>0.677</v>
       </c>
       <c r="D2">
         <v>0.7</v>
       </c>
       <c r="E2">
-        <v>0.712</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F2">
         <v>21</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>9</v>

--- a/data/analysis_pixtral_12b_no_reid/summary.xlsx
+++ b/data/analysis_pixtral_12b_no_reid/summary.xlsx
@@ -53,16 +53,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -78,7 +70,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -86,30 +78,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,34 +382,34 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -447,28 +421,28 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.677</v>
+        <v>0.765</v>
       </c>
       <c r="D2">
-        <v>0.7</v>
+        <v>0.433</v>
       </c>
       <c r="E2">
-        <v>0.6889999999999999</v>
+        <v>0.553</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I2">
         <v>30</v>
       </c>
       <c r="J2">
-        <v>636</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
